--- a/collections/phrasal_verbs.xlsx
+++ b/collections/phrasal_verbs.xlsx
@@ -7462,7 +7462,7 @@
       </c>
       <c r="F218" s="1" t="inlineStr">
         <is>
-          <t>The unreliable delivery service let's down on a busy day.</t>
+          <t>The delivery company let us down on our busiest day.</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F222" s="1" t="inlineStr">
         <is>
-          <t>The steward let's out through a gate beside the stage.</t>
+          <t>The steward let us out through a gate beside the stage.</t>
         </is>
       </c>
     </row>
